--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154200765</t>
+          <t>https://vimeo.com/1154202805</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154200948</t>
+          <t>https://vimeo.com/1154202922</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203167</t>
+          <t>https://vimeo.com/1154203273</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1154203167</t>
+          <t>https://vimeo.com/1154203273</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162061</t>
+          <t>https://vimeo.com/1192449734</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162237</t>
+          <t>https://vimeo.com/1192449909</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162517</t>
+          <t>https://vimeo.com/1192450070</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1177162727</t>
+          <t>https://vimeo.com/1192450190</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448619</t>
+          <t>https://vimeo.com/1192450344</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448625</t>
+          <t>https://vimeo.com/1192450466</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448633</t>
+          <t>https://vimeo.com/1192450581</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448640</t>
+          <t>https://vimeo.com/1192450716</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448644</t>
+          <t>https://vimeo.com/1192450836</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448654</t>
+          <t>https://vimeo.com/1192450930</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,295 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1192448660</t>
+          <t>https://vimeo.com/1192451107</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>34-year-old Male with Fluctuating Neuromuscular Symptoms</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>083498</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200663950</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>POCUS: Applications in Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>585111</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664146</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>93-year-old Female with Neck pain</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>083498</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664284</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Things We Do For No Kumu'ole (Reason) in Hospital Medicine</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>585111</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664448</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Teaching How to Think: Addressing Diagnostic Error on the Wards</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>083498</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664576</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>41-year-old Male with Joint pain</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>083498</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664727</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Do As Much Nothing As Possible: Minimizing Harm, Reducing Waste, and Maximizing Thriving in the Hospital</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>585111</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200665260</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>A Woman with Fever, Rash, and Gait Disturbance</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>083498</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200664888</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kuo Chiang Lian</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>総合内科</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Are You Happy? Physician Burnout and Wellness</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>585111</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1200665027</t>
         </is>
       </c>
     </row>
@@ -2473,6 +2761,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Do As Much Nothing As Possible: Minimizing Harm, Reducing Waste, and Maximizing Thriving in the Hospital</t>
+          <t>A Woman with Fever, Rash, and Gait Disturbance</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>585111</t>
+          <t>083498</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1200665260</t>
+          <t>https://vimeo.com/1200664888</t>
         </is>
       </c>
     </row>
@@ -2653,49 +2653,177 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>A Woman with Fever, Rash, and Gait Disturbance</t>
+          <t>Are You Happy? Physician Burnout and Wellness</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>585111</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1200664888</t>
+          <t>https://vimeo.com/1200665027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Dr. Kuo Chiang Lian</t>
+          <t>Dr. Shin Miyata</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>総合内科</t>
+          <t>小児外科</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Are You Happy? Physician Burnout and Wellness</t>
+          <t>Chest Wall Deformities</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>585111</t>
+          <t>795829</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1200665027</t>
+          <t>https://vimeo.com/1204023184</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Shin Miyata</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>小児外科</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Emesis in children</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>795829</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204023395</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Shin Miyata</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>小児外科</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Pediatric Trauma</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>795829</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204023561</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Shin Miyata</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>小児外科</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Commonな小児外科手術のHow I Do it</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>795829</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204023788</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Shin Miyata</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>小児外科</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Surgery for Anorectal Malformation and Hirschsprung's Disease</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>795829</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204024089</t>
         </is>
       </c>
     </row>
@@ -2770,6 +2898,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vimeo_links_omit.xlsx
+++ b/vimeo_links_omit.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>A Woman with Fever, Rash, and Gait Disturbance</t>
+          <t>Do As Much Nothing As Possible: Minimizing Harm, Reducing Waste, and Maximizing Thriving in the Hospital</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>083498</t>
+          <t>585111</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1200664888</t>
+          <t>https://vimeo.com/1204027316</t>
         </is>
       </c>
     </row>
@@ -2653,49 +2653,49 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Are You Happy? Physician Burnout and Wellness</t>
+          <t>A Woman with Fever, Rash, and Gait Disturbance</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>585111</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1200665027</t>
+          <t>https://vimeo.com/1200664888</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Dr. Shin Miyata</t>
+          <t>Dr. Kuo Chiang Lian</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>小児外科</t>
+          <t>総合内科</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+          <t>Assistant Professor of Medicine, University of Hawaii John A. Burns School of Medicine</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Chest Wall Deformities</t>
+          <t>Are You Happy? Physician Burnout and Wellness</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>795829</t>
+          <t>585111</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1204023184</t>
+          <t>https://vimeo.com/1200665027</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Emesis in children</t>
+          <t>Chest Wall Deformities</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1204023395</t>
+          <t>https://vimeo.com/1204023184</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Pediatric Trauma</t>
+          <t>Emesis in children</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1204023561</t>
+          <t>https://vimeo.com/1204023395</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Commonな小児外科手術のHow I Do it</t>
+          <t>Pediatric Trauma</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1204023788</t>
+          <t>https://vimeo.com/1204023561</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,81 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
+          <t>Commonな小児外科手術のHow I Do it</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>795829</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204023788</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Shin Miyata</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>小児外科</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
           <t>Surgery for Anorectal Malformation and Hirschsprung's Disease</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>795829</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>https://vimeo.com/1204024089</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Kana Miyata</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>腎臓内科</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Associate Professor Pediatric General and Thoracic Surgery, SSM Health Cardinal Glennon Children's Hospital St.Louis University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>The Reality of Internal Medicine Training in the United States</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>797308</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/1204027423</t>
         </is>
       </c>
     </row>
@@ -2902,6 +2966,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
